--- a/rosnedra_forecast/2026/rosnedra_page12.xlsx
+++ b/rosnedra_forecast/2026/rosnedra_page12.xlsx
@@ -1,34 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSOKIN\PROG\vgdb_tools\rosnedra_forecast\2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="7440"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Страница 12" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Страница 12" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+  <si>
+    <t>№ п/п</t>
+  </si>
+  <si>
+    <t>Субъект РФ</t>
+  </si>
+  <si>
+    <t>Наименование участка недр</t>
+  </si>
+  <si>
+    <t>Извлекаемые запасы и прогнозные ресурсы</t>
+  </si>
+  <si>
+    <t>Ханты-Мансийский автономный округ-Югра</t>
+  </si>
+  <si>
+    <t>нефть (извл.)
+Д0 - 8,563 млн.т.
+Д1 - 2,3 млн.т.
+Д2 - 0,6 млн.т.
+газ
+Д1 - 2,5 млрд.м3
+Д2 - 0,4 млрд.м3</t>
+  </si>
+  <si>
+    <t>Шаймский 3</t>
+  </si>
+  <si>
+    <t>нефть (извл.)
+Д0 - 1.127 млн.т.
+Д1 - 0.597 млн.т.
+Д1 - 0.4 млн.т.
+Д2 - 0.2 млн.т.</t>
+  </si>
+  <si>
+    <t>Шебурский</t>
+  </si>
+  <si>
+    <t>нефть (извл.)
+Д0 - 1,080 млн.т.
+Д1 - 0,5 млн.т.
+Д1 - 1,0 млн.т.
+Д2 - 0,3 млн.т.
+газ
+Д1 - 0,3 млрд.м3
+Д2 - 0,8 млрд.м3</t>
+  </si>
+  <si>
+    <t>Шугурский</t>
+  </si>
+  <si>
+    <t>нефть (извл.)
+Д0 - 0,665 млн.т.
+Д1 - 1,2 млн.т.
+Д2 - 0,3 млн.т.
+газ
+Д1 - 0,2 млрд.м3
+Д2 - 0,6 млрд.м3</t>
+  </si>
+  <si>
+    <t>Южно-Айтульский</t>
+  </si>
+  <si>
+    <t>нефть (извл.):
+Д0 - 3,760 млн.т.
+Д1 - 5,786 млн.т.
+Д2 - 10,0 млн.т.
+Д2 - 0,7 млн.т.
+газ (извл.):
+Д1 - 5,0 млрд.м3.
+Д2 - 3,9 млрд.м3.</t>
+  </si>
+  <si>
+    <t>Южно-Серинский</t>
+  </si>
+  <si>
+    <t>нефть (извл.)
+Д1 - 11.5 млн.т.
+Д2 - 0.4 млн.т.
+газ
+Д1 - 0.4 млрд.м3
+Д2 - 0.8 млрд.м3</t>
+  </si>
+  <si>
+    <t>Южно-Ташинский</t>
+  </si>
+  <si>
+    <t>нефть (извл.)
+Д1 - 11.6 млн.т.
+Д2 - 0.6 млн.т.</t>
+  </si>
+  <si>
+    <t>Токушинский</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,83 +149,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -411,253 +454,126 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="90" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="3" max="3" width="35" customWidth="1"/>
+    <col min="4" max="4" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>№ п/п</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Субъект РФ</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Наименование участка недр</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Извлекаемые запасы и природные ресурсы (с указанием категории) (ед.изм)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>103</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Терпеевский 2</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 7,4 млн т
-D2 - 0,3 млн т
-газ
-D1 - 0,2 млрд м3
-D2 - 0,5 млрд м3</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>104</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Терпеевский 3</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 6,9 млн т
-D2 - 0,3 млн т
-газ
-D1 - 0,2 млрд м3
-D2 - 0,4 млрд м3</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>105</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Торъеганский</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 12,7 млн т
-D2 - 0,5 млн т
-газ
-D1 - 0,4 млрд м3
-D2 - 0,9 млрд м3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>106</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Тундринский 4</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 4,8 млн т
-D2 - 0,2 млн т</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>107</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Тундринский 5</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 5,1 млн т
-D2 - 0,2 млн т</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>108</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Тундринский 6</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 5,6 млн т
-D2 - 0,3 млн т</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>109</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Усть-Тегусский 7</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 14,8 млн т
-D2 - 0,6 млн т
-газ
-D1 - 0,5 млрд м3
-D2 - 1,0 млрд м3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Усть-Тегусский 8</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 16,1 млн т
-D2 - 0,7 млн т
-газ
-D1 - 0,6 млрд м3
-D2 - 1,1 млрд м3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Ханты-Мансийский автономный округ-Югра</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Шеркалинский</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>нефть (извл.)
-D1 - 3,7 млн т
-D2 - 0,1 млн т</t>
-        </is>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
